--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23D.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23D.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="7365"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -109,31 +109,31 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Departamento de Información y Relaciones Publicas del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>AEFD86248543F6AF86D51A02DE5FECDD</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>03/04/2023</t>
-  </si>
-  <si>
-    <t>28/06/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo 01 de abril de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no tiene inherencia en la utilización de Tiempos Oficiales por lo que hago mención de dos mensajes aclaratorios e informativos: Menasje 1:"La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales está a cargo de la Dirección General de Radio, Televisión y Cinematografía de la Secretaría de Gabernación." Mensaje 2:" La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales esta a cargo del Instituto Nacional Electoral." Por lo que no se genera información alguna.</t>
+    <t>88CA33925C2C4E0E7F5EBE7FC7EEFCD6</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>01/01/2022</t>
+  </si>
+  <si>
+    <t>31/03/2022</t>
+  </si>
+  <si>
+    <t>La publicación y actualización de la información relativa a la utilización de los tiempos oficiales esta a cargo del Instituto Nacional Electoral</t>
+  </si>
+  <si>
+    <t>https://www.ine.mx/actores-politicos/administracion-tiempos-estado/</t>
+  </si>
+  <si>
+    <t>Departamento de Información y Relaciones Públicas del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>03/05/2022</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 1 de enero de 2021 al 31 de marzo de 2021, el Colegio de Bachilleres del Estado de Tlaxcala no tiene autorizado Programa Anual de Trabajo para el Departamento de Información y Relaciones Públicas.</t>
   </si>
 </sst>
 </file>
@@ -529,16 +529,16 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="117.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="116.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="86" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="255" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="189.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
@@ -681,28 +681,28 @@
     </row>
     <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>38</v>
